--- a/order_forms/018_high_visibility_gear_order_form--order_forms.xlsx
+++ b/order_forms/018_high_visibility_gear_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,40 +515,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>high_visibility_gear_order_form_page_1</t>
+          <t>order_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>order_details</t>
+          <t>What is the order type?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_info</t>
+          <t>high_visibility_item_size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_info</t>
+          <t>What is the size of the item?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>delivery_info</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>delivery_info</t>
+          <t>What is the color of the item?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>payment_details</t>
+          <t>fabric_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>payment_details</t>
+          <t>What type of fabric is the item made of?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>order_items</t>
+          <t>order_quantity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>order_items</t>
+          <t>How many items do you need?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,46 +630,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>order_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>What is the delivery date?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submit_button</t>
+          <t>order_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>What is the delivery time?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is the customer's email address?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What is the customer's phone number?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>What is the customer's address?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>What is the customer's city?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>What is the customer's state?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>What is the customer's zip code?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,13 +824,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>What is the customer's country?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,58 +842,58 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>order_quantity</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>submit_button</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>Submit Button</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>order_time</t>
+          <t>high_visibility_item_type</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>order_time</t>
+          <t>What type of high visibility item?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>submit_button_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>Submit Button 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,40 +929,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submit_button_2</t>
+          <t>high_visibility_item_size_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>What is the size of the high visibility item?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>high_visibility_item_type</t>
+          <t>high_visibility_item_size2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>high_visibility_item_type</t>
+          <t>High Visibility Item Size2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,17 +975,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>high_visibility_item_size</t>
+          <t>color2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>high_visibility_item_size</t>
+          <t>What is the color of the high visibility item?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,87 +1003,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>fabric_type2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>What type of fabric is the high visibility item made of?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fabric_type</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>fabric_type</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submit_button_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit_button_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,10 +1029,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1057,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>high_visibility_item_type_choices</t>
+          <t>order_details_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1136,14 +1067,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>reflective_jacket</t>
+          <t>reflective jacket</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>high_visibility_item_type_choices</t>
+          <t>order_details_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1153,31 +1084,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>safety_gloves</t>
+          <t>safety gloves</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>high_visibility_item_type_choices</t>
+          <t>order_details_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>safety_vests</t>
+          <t>safety_vest</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>safety_vests</t>
+          <t>safety vest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>high_visibility_item_type_choices</t>
+          <t>order_details_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1187,14 +1118,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>safety_helmet</t>
+          <t>safety helmet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>high_visibility_item_type_choices</t>
+          <t>order_details_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1204,7 +1135,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>reflective_vest</t>
+          <t>reflective vest</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1152,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>extra_small</t>
+          <t>extra small</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1220,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>extra_large</t>
+          <t>extra large</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1237,296 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>x large</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>high_visibility_item_type_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reflective_jacket</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>reflective jacket</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>high_visibility_item_type_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>safety_gloves</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>safety gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>high_visibility_item_type_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>safety_vest</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>safety vest</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>high_visibility_item_type_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>safety_helmet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>safety helmet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>high_visibility_item_type_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reflective_vest</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>reflective vest</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>extra_small</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>extra small</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>extra_large</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>extra large</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>x_large</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>x large</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>extra_small</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>extra small</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size2_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size2_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>extra_large</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>extra large</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>high_visibility_item_size2_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>x_large</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>x large</t>
         </is>
       </c>
     </row>
